--- a/utils/monday_sprint_sprint_2023-04.xlsx
+++ b/utils/monday_sprint_sprint_2023-04.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="150">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>16359</t>
+    <t>3856515575</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>23/01/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>20/02/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>17485</t>
+    <t>3876885317</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -117,7 +117,10 @@
     <t>26/01/2023</t>
   </si>
   <si>
-    <t>17758</t>
+    <t>25/02/2023</t>
+  </si>
+  <si>
+    <t>3895774131</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -129,10 +132,13 @@
     <t>30/01/2023</t>
   </si>
   <si>
+    <t>26/02/2023</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>6609</t>
+    <t>3903401761</t>
   </si>
   <si>
     <t>Indefinido</t>
@@ -144,13 +150,16 @@
     <t>31/01/2023</t>
   </si>
   <si>
-    <t>15543</t>
+    <t>3903420916</t>
   </si>
   <si>
     <t>Saldo de peças por Setor</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>14/02/2023</t>
+  </si>
+  <si>
+    <t>3938716101</t>
   </si>
   <si>
     <t>Análise</t>
@@ -162,13 +171,16 @@
     <t>06/02/2023</t>
   </si>
   <si>
+    <t>19/02/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>18530</t>
+    <t>3961346667</t>
   </si>
   <si>
     <t>Alteração de regra no relatório de vida útil dos modelos</t>
@@ -180,22 +192,25 @@
     <t>09/02/2023</t>
   </si>
   <si>
+    <t>13/02/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>18524</t>
+    <t>3961370515</t>
   </si>
   <si>
     <t>FTFu no registro de moldagem USE e ULE</t>
   </si>
   <si>
-    <t>18494</t>
+    <t>3961388879</t>
   </si>
   <si>
     <t>Alteração no setor 501 - Alerta de revisão</t>
   </si>
   <si>
-    <t>18473</t>
+    <t>3965146188</t>
   </si>
   <si>
     <t>Observações ao inserir setor no fluxo no PCP</t>
@@ -204,141 +219,144 @@
     <t>10/02/2023</t>
   </si>
   <si>
-    <t>18447</t>
+    <t>3965256265</t>
   </si>
   <si>
     <t>Melhoria na pré-lista de EPIs para agilidade no preenchimento dos colaboradores</t>
   </si>
   <si>
-    <t>18429</t>
+    <t>3965270393</t>
   </si>
   <si>
     <t>Melhorias apontamento de moldagem USE/ULE</t>
   </si>
   <si>
-    <t>18380</t>
+    <t>3965342774</t>
   </si>
   <si>
     <t>Colocar opção de moeda na CPC</t>
   </si>
   <si>
-    <t>18371</t>
+    <t>3965361884</t>
   </si>
   <si>
     <t>Projeto FATURA - Inserção de dados no "Planilha MPS + Cenários"</t>
   </si>
   <si>
-    <t>18366</t>
+    <t>3965380924</t>
   </si>
   <si>
     <t>Tela para dupla checagem no envio de OC</t>
   </si>
   <si>
-    <t>18344</t>
+    <t>3965399402</t>
   </si>
   <si>
     <t>Inclusão de colunas - relatórios invoices a vencer e vencidas</t>
   </si>
   <si>
-    <t>18315</t>
+    <t>3965435863</t>
   </si>
   <si>
     <t>Automatizar geração do relatório de gestão de estoques</t>
   </si>
   <si>
-    <t>18280</t>
+    <t>3965448505</t>
   </si>
   <si>
     <t>Exclusão do cadastro de limitadores</t>
   </si>
   <si>
-    <t>18086</t>
+    <t>3965535907</t>
   </si>
   <si>
     <t>Log de alterações no sistema de Compras</t>
   </si>
   <si>
-    <t>18059</t>
+    <t>18/02/2023</t>
+  </si>
+  <si>
+    <t>3965584461</t>
   </si>
   <si>
     <t>Novo relatório baseado no log de eventos do saldo de depósito</t>
   </si>
   <si>
-    <t>18591</t>
+    <t>3966642309</t>
   </si>
   <si>
     <t>Adequar SICs de valores mensais por longos períodos à meta da conta contábil</t>
   </si>
   <si>
-    <t>18569</t>
+    <t>23/02/2023</t>
+  </si>
+  <si>
+    <t>3966661424</t>
   </si>
   <si>
     <t>Inclusão de setores no controle de radiografia</t>
   </si>
   <si>
-    <t>18587</t>
+    <t>3966681052</t>
   </si>
   <si>
     <t>Inclusão de colunas no relatório de faturamento Modelos por Cliente</t>
   </si>
   <si>
-    <t>18590</t>
+    <t>3966711428</t>
   </si>
   <si>
     <t>Carteira com Serviços em Terceiros</t>
   </si>
   <si>
-    <t>18595</t>
+    <t>3966724606</t>
   </si>
   <si>
     <t>Vínculo do apontamento de inspeção a seq. de pré-produtivo</t>
   </si>
   <si>
-    <t>18662</t>
+    <t>3967115206</t>
   </si>
   <si>
     <t>Análise da automação da integração das notas de entrada.</t>
   </si>
   <si>
-    <t>18491</t>
+    <t>3967562869</t>
   </si>
   <si>
     <t>Criar uma tela de consulta para registros considerando filtros de ressalva.</t>
   </si>
   <si>
-    <t>18572</t>
+    <t>3967875777</t>
   </si>
   <si>
     <t>Realizar alterações no layout do CPP/OTF.</t>
   </si>
   <si>
-    <t>18490</t>
+    <t>3967929038</t>
   </si>
   <si>
     <t>Registro de moldagem USE e ULE- Tempo de retrabalho.</t>
   </si>
   <si>
-    <t>18489</t>
+    <t>3967942703</t>
   </si>
   <si>
     <t>Registro de moldagem USE e USE - Criar registro para preparação de moldes</t>
   </si>
   <si>
-    <t>18488</t>
+    <t>3967947484</t>
   </si>
   <si>
     <t>Registro de moldagem USE e ULE - criar correlação de peso de conjunto.</t>
   </si>
   <si>
-    <t>18545</t>
+    <t>3975385743</t>
   </si>
   <si>
     <t>Apontamento Ajustagem.</t>
   </si>
   <si>
-    <t>13/02/2023</t>
-  </si>
-  <si>
     <t>3977796237</t>
   </si>
   <si>
@@ -360,7 +378,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-04</t>
+    <t>Jan/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -418,6 +436,9 @@
   </si>
   <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1002,7 +1023,7 @@
         <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1019,22 +1040,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1046,10 +1067,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1058,7 +1079,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1066,22 +1087,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>32</v>
@@ -1093,7 +1114,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1105,7 +1126,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1113,7 +1134,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1125,10 +1146,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>32</v>
@@ -1140,10 +1161,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1152,7 +1173,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1160,22 +1181,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1187,10 +1208,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1199,33 +1220,33 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>21</v>
@@ -1234,27 +1255,27 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1266,14 +1287,14 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
       </c>
@@ -1281,27 +1302,27 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1313,13 +1334,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>21</v>
@@ -1328,89 +1349,89 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="O11" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>32</v>
@@ -1422,10 +1443,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1434,30 +1455,30 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
@@ -1469,10 +1490,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1481,30 +1502,30 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -1516,10 +1537,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1528,15 +1549,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1548,13 +1569,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1563,10 +1584,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1575,15 +1596,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1595,13 +1616,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1610,10 +1631,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1622,15 +1643,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1642,13 +1663,13 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1657,10 +1678,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1669,33 +1690,33 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1704,7 +1725,7 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>24</v>
@@ -1716,33 +1737,33 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -1751,10 +1772,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1763,15 +1784,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1783,13 +1804,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
@@ -1798,10 +1819,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1810,15 +1831,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1830,13 +1851,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1845,10 +1866,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1857,30 +1878,30 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1892,10 +1913,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1904,33 +1925,33 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -1939,10 +1960,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1951,15 +1972,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1971,13 +1992,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -1986,10 +2007,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1998,33 +2019,33 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -2033,10 +2054,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2045,33 +2066,33 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2080,10 +2101,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2092,15 +2113,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2112,10 +2133,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2127,10 +2148,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2139,30 +2160,30 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -2174,10 +2195,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2186,15 +2207,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2206,10 +2227,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -2221,10 +2242,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2233,30 +2254,30 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
@@ -2268,10 +2289,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2280,30 +2301,30 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -2315,10 +2336,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2327,30 +2348,30 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>32</v>
@@ -2362,10 +2383,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2374,30 +2395,30 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>32</v>
@@ -2409,10 +2430,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2421,33 +2442,33 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2456,10 +2477,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2468,33 +2489,33 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2503,10 +2524,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2515,33 +2536,33 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>21</v>
@@ -2550,10 +2571,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2562,10 +2583,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2581,23 +2602,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2605,16 +2626,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2625,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>11.83</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2633,7 +2654,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2646,7 +2667,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2654,7 +2675,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2685,12 +2706,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B2">
         <v>35</v>
@@ -2704,7 +2725,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2714,25 +2735,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2743,19 +2764,19 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2767,10 +2788,10 @@
         <v>35</v>
       </c>
       <c r="P10" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -2793,21 +2814,21 @@
         <v>35</v>
       </c>
       <c r="M11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="Q11">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -2819,13 +2840,13 @@
         <v>12</v>
       </c>
       <c r="J12" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2834,10 +2855,10 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>17</v>
       </c>
@@ -2845,39 +2866,33 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H13">
         <v>15</v>
       </c>
       <c r="M13" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2885,7 +2900,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2893,7 +2908,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2901,7 +2916,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2909,10 +2924,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2920,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2928,142 +2943,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
